--- a/Dados Integrador/temperatura.xlsx
+++ b/Dados Integrador/temperatura.xlsx
@@ -80,7 +80,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -500,7 +500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -540,7 +540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -560,7 +560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -580,7 +580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -600,7 +600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -620,7 +620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -640,7 +640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
@@ -660,7 +660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
@@ -680,7 +680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
@@ -700,7 +700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
@@ -720,7 +720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
@@ -740,7 +740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
@@ -800,7 +800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>

--- a/Dados Integrador/temperatura.xlsx
+++ b/Dados Integrador/temperatura.xlsx
@@ -820,7 +820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
@@ -840,7 +840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -860,7 +860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
@@ -880,7 +880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -900,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -920,7 +920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
@@ -940,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>6</v>
       </c>
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
         <v>6</v>
       </c>
